--- a/output/pdf_financials_xlsx/SRI.xlsx
+++ b/output/pdf_financials_xlsx/SRI.xlsx
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.037813999999999</v>
+        <v>0.446</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.016863</v>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.795907</v>
+        <v>-3.795907</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.751984</v>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.795907</v>
+        <v>-3.795907</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-2.751984</v>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>63.3648</v>
+        <v>-63.3648</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>67.894201</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.037813999999999</v>
+        <v>0.446</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.016863</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.044955</v>
+        <v>0.453141</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0.132272</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>52.77438617017015</v>
+        <v>951.1002242152466</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-16219.65842376801</v>
@@ -6251,52 +6251,52 @@
         <v>4.190316</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.322164</v>
+        <v>0.971984</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.852282</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.394689</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.340351</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.287999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.350083</v>
+        <v>0.509641</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.350083</v>
+        <v>0.509641</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.350083</v>
+        <v>0.509641</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.350083</v>
+        <v>0.500441</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.350083</v>
+        <v>0.476119</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.354018</v>
+        <v>0.591707</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.354018</v>
+        <v>0.602373</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.354018</v>
+        <v>0.369355</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0.354018</v>
+        <v>0.481958</v>
       </c>
     </row>
     <row r="93">
@@ -10460,7 +10460,11 @@
           <t>Share-based payment reserve 8(b)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -17302,7 +17306,11 @@
           <t>Share-based payment reserve 8(a)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -20726,7 +20734,11 @@
           <t>Share-based payment reserve 9(b) 159,558</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -22826,7 +22838,11 @@
           <t>Share-based payment reserve 10(b)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -23652,7 +23668,11 @@
           <t>Share-based payment reserve 11 (b)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -27760,7 +27780,11 @@
           <t>Share-based payment reserve 13 (b)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -31592,7 +31616,11 @@
           <t>Share-based payment reserve 13 (b) 852,282</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -73671,10 +73699,10 @@
         </is>
       </c>
       <c r="F624" s="5" t="n">
-        <v>3.795907</v>
+        <v>-3.795907</v>
       </c>
       <c r="G624" s="5" t="n">
-        <v>2.664202</v>
+        <v>-2.664202</v>
       </c>
       <c r="H624" t="inlineStr">
         <is>
@@ -75908,10 +75936,10 @@
         </is>
       </c>
       <c r="E645" s="5" t="n">
-        <v>1.267296</v>
+        <v>-1.267296</v>
       </c>
       <c r="F645" s="5" t="n">
-        <v>3.795907</v>
+        <v>-3.795907</v>
       </c>
       <c r="G645" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SRI.xlsx
+++ b/output/pdf_financials_xlsx/SRI.xlsx
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023305</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001236</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000408</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2190,13 +2190,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.267296</v>
+        <v>-1.243991</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.446</v>
+        <v>0.447236</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.016863</v>
+        <v>-0.016455</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.173067</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.267296</v>
+        <v>-1.243991</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.453141</v>
+        <v>0.454377</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.132272</v>
+        <v>0.13268</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.173067</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>135.690031903653</v>
+        <v>136.1085750043598</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2619,58 +2619,58 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.603511</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.87339</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.87339</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.457835</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.297121</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.028118</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.015406</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.036183</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.464066</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.124049</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.030117</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004093</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.10284</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.236447</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.080556</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.411406</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.005253</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.284485</v>
       </c>
     </row>
     <row r="35">
@@ -2741,58 +2741,58 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.603511</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.87339</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.87339</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.02825</v>
+        <v>0.486085</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.019233</v>
+        <v>0.316354</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.0059</v>
+        <v>0.034018</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.00645</v>
+        <v>0.021856</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.004658</v>
+        <v>0.040841</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.032883</v>
+        <v>0.496949</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.06745</v>
+        <v>0.191499</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.002017</v>
+        <v>0.032134</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.001276</v>
+        <v>0.005369</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.002292</v>
+        <v>0.105132</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.009658</v>
+        <v>0.246105</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.004836</v>
+        <v>0.085392</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.001496</v>
+        <v>0.40991</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.005253</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.284485</v>
       </c>
     </row>
     <row r="37">
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.978066</v>
+        <v>0.374555</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.21495</v>
+        <v>0.34156</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.982534</v>
+        <v>0.109144</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.626367</v>
+        <v>0.168532</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.416563</v>
+        <v>0.119442</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.03303</v>
+        <v>0.004912</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.015406</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.028153</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.679702</v>
+        <v>2.215636</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.113058</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.041004</v>
+        <v>0.010887</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.010479</v>
+        <v>0.006386</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.104153</v>
+        <v>0.001313</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.246617</v>
+        <v>0.01017</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.09202</v>
+        <v>0.011464</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.424193</v>
+        <v>0.012787</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.014876</v>
+        <v>0.009623</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.294586</v>
+        <v>0.010101</v>
       </c>
     </row>
     <row r="49">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -28834,7 +28834,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -32450,7 +32450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -35010,7 +35010,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E253" s="5" t="n">
@@ -64330,7 +64330,11 @@
           <t>General and administrative expenses 11&amp;9</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr"/>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -65708,7 +65712,11 @@
           <t>General and administrative expenses 5 &amp; 12</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -72620,7 +72628,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -74862,7 +74870,7 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E635" s="5" t="n">
@@ -75078,7 +75086,7 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E637" s="5" t="n">

--- a/output/pdf_financials_xlsx/SRI.xlsx
+++ b/output/pdf_financials_xlsx/SRI.xlsx
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.039152</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.04676</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.039124</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -926,19 +926,19 @@
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="M9" s="1" t="inlineStr">
         <is>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0</v>
+        <v>0.018724</v>
       </c>
     </row>
     <row r="10">
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.017358</v>
+        <v>0.035358</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.786768</v>
@@ -1028,7 +1028,7 @@
         <v>0.940779</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.030269</v>
+        <v>0.048993</v>
       </c>
     </row>
     <row r="11">
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.014121</v>
+        <v>-0.003879</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.770879</v>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.030269</v>
+        <v>-0.048993</v>
       </c>
     </row>
     <row r="12">
@@ -2304,13 +2304,13 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.044912</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.020723</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.020483</v>
       </c>
     </row>
     <row r="29">
@@ -2369,13 +2369,13 @@
         <v>-0.351011</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.333367</v>
+        <v>-0.288455</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.771662</v>
+        <v>-0.750939</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.369516</v>
+        <v>-0.349033</v>
       </c>
     </row>
     <row r="30">
@@ -2446,7 +2446,7 @@
         <v>-105.3944662132745</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-729.707781547554</v>
+        <v>-631.3998029987961</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -6728,13 +6728,13 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.044912</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.020723</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.020483</v>
       </c>
     </row>
     <row r="101">
@@ -37224,7 +37224,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -56296,7 +56300,11 @@
           <t>Occupancy costs 9</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -58626,7 +58634,11 @@
           <t>Occupancy costs 9</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -60468,7 +60480,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -66140,7 +66156,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -74660,7 +74680,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E633" s="5" t="n">
         <v>0.039152</v>
       </c>

--- a/output/pdf_financials_xlsx/SRI.xlsx
+++ b/output/pdf_financials_xlsx/SRI.xlsx
@@ -1452,7 +1452,7 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.018381</v>
+        <v>-0.018381</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2994,13 +2994,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.30316</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.005098</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.00011</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -3055,13 +3055,13 @@
         <v>0.071136</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.351187</v>
+        <v>0.654347</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.060897</v>
+        <v>0.065995</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.028361</v>
+        <v>0.028471</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.370207</v>
@@ -3482,13 +3482,13 @@
         <v>0.109144</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.168532</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.119442</v>
+        <v>0.114344</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.004912</v>
+        <v>0.004802</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013818</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.052178</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-0.029239</v>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.019221</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.00603</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7628,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.026491</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.004571</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013818</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.052178</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-0.029239</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.705157</v>
+        <v>-0.718975</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.28766</v>
+        <v>-1.339838</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-2.490686</v>
@@ -37032,7 +37032,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -37770,7 +37774,11 @@
           <t>Shares issued for cash 8(a)</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -38842,7 +38850,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39658,7 +39670,11 @@
           <t>Shares issued for cash 8</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -40178,7 +40194,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -41832,7 +41852,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -43096,7 +43120,11 @@
           <t>Net Income (loss)</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -49818,7 +49846,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -50560,7 +50592,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -51300,7 +51336,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -51510,7 +51550,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -54180,7 +54224,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E437" s="5" t="n">
         <v>-0.013818</v>
       </c>
@@ -54284,7 +54332,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E438" s="5" t="n">
         <v>0.019221</v>
       </c>
@@ -67112,7 +67164,11 @@
           <t>Income taxes recovery 18</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E561" t="inlineStr">
         <is>
           <t>-</t>
